--- a/artfynd/A 28173-2026 artfynd.xlsx
+++ b/artfynd/A 28173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135999553</v>
       </c>
       <c r="B2" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136032180</v>
       </c>
       <c r="B3" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135999555</v>
       </c>
       <c r="B4" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135999556</v>
       </c>
       <c r="B5" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28173-2026 artfynd.xlsx
+++ b/artfynd/A 28173-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>136032180</v>
       </c>
       <c r="B3" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
